--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2024_valparaiso.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2024_valparaiso.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:43</t>
+    <t xml:space="preserve">2026-10-05 02:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>261599.59</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -767,7 +767,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>265065.62</v>
+        <v>265065.63</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>312437.25</v>
@@ -847,7 +847,7 @@
         <v>277477.34</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -913,7 +913,7 @@
         <v>280666.56</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -1042,7 +1042,7 @@
         <v>34</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>259413.62</v>
+        <v>259413.63</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>305883.38</v>
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>282587.62</v>
+        <v>282587.63</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>336761.47</v>
@@ -1130,7 +1130,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>285626.12</v>
+        <v>285626.13</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>338820.44</v>
@@ -1287,7 +1287,7 @@
         <v>337370.19</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1317,7 +1317,7 @@
         <v>59</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>361755.62</v>
+        <v>361755.63</v>
       </c>
       <c r="C58" s="2" t="n">
         <v>418300.28</v>
@@ -1526,10 +1526,10 @@
         <v>78</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>383199.62</v>
+        <v>383199.63</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1595,7 +1595,7 @@
         <v>392259.53</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
